--- a/ML-Entrees/ig/StructureDefinition-fr-lm-corps-document.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-corps-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T10:50:27+00:00</t>
+    <t>2026-04-07T13:39:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-corps-document.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-corps-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T13:39:53+00:00</t>
+    <t>2026-04-08T09:43:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-corps-document.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-corps-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T09:43:36+00:00</t>
+    <t>2026-04-08T13:03:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-corps-document.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-corps-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T13:03:38+00:00</t>
+    <t>2026-04-08T14:07:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-corps-document.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-corps-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T14:07:03+00:00</t>
+    <t>2026-04-09T12:24:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-corps-document.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-corps-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-09T12:24:05+00:00</t>
+    <t>2026-04-13T08:58:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-corps-document.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-corps-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-13T08:58:24+00:00</t>
+    <t>2026-04-13T09:04:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-corps-document.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-corps-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-13T09:04:52+00:00</t>
+    <t>2026-04-14T07:59:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-corps-document.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-corps-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-14T07:59:58+00:00</t>
+    <t>2026-04-16T07:11:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-corps-document.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-corps-document.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1561" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1530" uniqueCount="216">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0-snapsnot</t>
+    <t>0.1.0-snapshot</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T07:11:11+00:00</t>
+    <t>2026-04-24T08:31:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -510,10 +510,10 @@
     <t>Section Historique des actes</t>
   </si>
   <si>
-    <t>fr-lm-corps-document.historiqueDesGrossesses</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-historique-des-grossesses
+    <t>fr-lm-corps-document.pregnancyHistory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-section-pregnancy-history
 </t>
   </si>
   <si>
@@ -528,16 +528,6 @@
   </si>
   <si>
     <t>Section Plan de Soins</t>
-  </si>
-  <si>
-    <t>fr-lm-corps-document.pointsDeVigilancesNonCode</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-points-de-vigilances-non-code
-</t>
-  </si>
-  <si>
-    <t>Section Points de Vigilances non code</t>
   </si>
   <si>
     <t>fr-lm-corps-document.prescriptionDispositifsMedicaux</t>
@@ -1019,7 +1009,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ49"/>
+  <dimension ref="A1:AJ48"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="54.4765625" customWidth="true" bestFit="true"/>
@@ -5869,106 +5859,6 @@
         <v>73</v>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="B49" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="C49" s="2"/>
-      <c r="D49" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E49" s="2"/>
-      <c r="F49" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G49" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H49" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I49" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J49" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K49" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="L49" t="s" s="2">
-        <v>218</v>
-      </c>
-      <c r="M49" t="s" s="2">
-        <v>218</v>
-      </c>
-      <c r="N49" s="2"/>
-      <c r="O49" s="2"/>
-      <c r="P49" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q49" s="2"/>
-      <c r="R49" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S49" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T49" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U49" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V49" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W49" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X49" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y49" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z49" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA49" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB49" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC49" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD49" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE49" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF49" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="AG49" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH49" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI49" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AJ49" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-corps-document.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-corps-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-24T08:31:26+00:00</t>
+    <t>2026-04-24T12:30:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-corps-document.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-corps-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-24T12:30:57+00:00</t>
+    <t>2026-04-24T12:43:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
